--- a/QuestionsBin.xlsx
+++ b/QuestionsBin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priya\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6E6412-F074-4A02-868D-FCE891C487F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5F00D6-44C1-4255-A289-E74DB83B03D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11775" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19306,7 +19306,7 @@
     <t>13 अंग, 12 पूर्व</t>
   </si>
   <si>
-    <t>This game wouldn't be possible without Vikas Jain (Indore)! We are deeply grateful to him for bringing this idea to life and dedicating his time to write most of our questions. Thank you so much, Vikasji. Jai Jinendra.</t>
+    <t>We are deeply grateful to Vikas Jain (Indore) for bringing this idea to life and dedicating his time and knowledge to design most of the questions. Thank you so much, Vikasji. Jai Jinendra.</t>
   </si>
 </sst>
 </file>
@@ -19832,7 +19832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -20404,7 +20404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>12</v>
       </c>
@@ -20456,7 +20456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>13</v>
       </c>
@@ -21964,7 +21964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>42</v>
       </c>
@@ -23084,7 +23084,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A129" s="10">
         <v>64</v>
       </c>
@@ -24020,7 +24020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A165" s="10">
         <v>82</v>
       </c>
@@ -24332,7 +24332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A177" s="10">
         <v>88</v>
       </c>
@@ -24436,7 +24436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A181" s="10">
         <v>90</v>
       </c>
@@ -24748,7 +24748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A193" s="10">
         <v>96</v>
       </c>
@@ -26360,7 +26360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="255" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A255" s="5">
         <v>130</v>
       </c>
@@ -26672,7 +26672,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="267" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A267" s="5">
         <v>136</v>
       </c>
@@ -26776,7 +26776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A271" s="5">
         <v>138</v>
       </c>
@@ -27088,7 +27088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A283" s="5">
         <v>144</v>
       </c>
@@ -28076,7 +28076,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="321" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A321" s="5">
         <v>166</v>
       </c>
@@ -28648,7 +28648,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="343" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A343" s="5">
         <v>178</v>
       </c>
@@ -28856,7 +28856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="351" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A351" s="5">
         <v>182</v>
       </c>
@@ -29064,7 +29064,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="359" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A359" s="5">
         <v>186</v>
       </c>
@@ -29948,7 +29948,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="393" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A393" s="5">
         <v>203</v>
       </c>
@@ -30000,7 +30000,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="395" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A395" s="5">
         <v>204</v>
       </c>
@@ -30052,7 +30052,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="397" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A397" s="5">
         <v>205</v>
       </c>
@@ -30208,7 +30208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="403" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A403" s="5">
         <v>208</v>
       </c>
@@ -30364,7 +30364,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A409" s="5">
         <v>211</v>
       </c>
@@ -30416,7 +30416,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="411" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A411" s="5">
         <v>212</v>
       </c>
@@ -30520,7 +30520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="415" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A415" s="5">
         <v>214</v>
       </c>
@@ -30572,7 +30572,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A417" s="5">
         <v>215</v>
       </c>
@@ -30624,7 +30624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="419" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A419" s="5">
         <v>216</v>
       </c>
@@ -30676,7 +30676,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="421" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A421" s="5">
         <v>217</v>
       </c>
@@ -30988,7 +30988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="433" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A433" s="5">
         <v>223</v>
       </c>
@@ -31040,7 +31040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="435" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A435" s="5">
         <v>224</v>
       </c>
@@ -31092,7 +31092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="437" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A437" s="5">
         <v>225</v>
       </c>
@@ -31144,7 +31144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="439" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A439" s="5">
         <v>226</v>
       </c>
@@ -31352,7 +31352,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="447" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A447" s="5">
         <v>230</v>
       </c>
@@ -31404,7 +31404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="449" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A449" s="5">
         <v>231</v>
       </c>
@@ -31456,7 +31456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="451" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A451" s="5">
         <v>232</v>
       </c>
@@ -31664,7 +31664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="459" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A459" s="5">
         <v>236</v>
       </c>
@@ -31768,7 +31768,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="463" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A463" s="5">
         <v>238</v>
       </c>
@@ -31820,7 +31820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="465" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A465" s="5">
         <v>239</v>
       </c>
@@ -32184,7 +32184,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="479" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A479" s="5">
         <v>246</v>
       </c>
@@ -32704,7 +32704,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="499" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A499" s="5">
         <v>256</v>
       </c>
@@ -32756,7 +32756,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="501" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A501" s="5">
         <v>257</v>
       </c>
@@ -33068,7 +33068,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="513" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A513" s="5">
         <v>263</v>
       </c>
@@ -33328,7 +33328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="523" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A523" s="5">
         <v>268</v>
       </c>
@@ -34472,7 +34472,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="567" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A567" s="5">
         <v>290</v>
       </c>
@@ -35148,7 +35148,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="593" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A593" s="5">
         <v>304</v>
       </c>
@@ -36552,7 +36552,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="647" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A647" s="5">
         <v>331</v>
       </c>
@@ -36916,7 +36916,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="661" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A661" s="5">
         <v>338</v>
       </c>
@@ -37020,7 +37020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="665" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A665" s="5">
         <v>340</v>
       </c>
@@ -37592,7 +37592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="687" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A687" s="5">
         <v>351</v>
       </c>
@@ -37696,7 +37696,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="691" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A691" s="5">
         <v>353</v>
       </c>
@@ -38892,7 +38892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="737" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A737" s="5">
         <v>376</v>
       </c>
@@ -39100,7 +39100,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="745" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A745" s="5">
         <v>380</v>
       </c>
@@ -39724,7 +39724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="769" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A769" s="5">
         <v>393</v>
       </c>
@@ -39776,7 +39776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="771" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A771" s="5">
         <v>394</v>
       </c>
@@ -40400,7 +40400,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="795" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A795" s="5">
         <v>408</v>
       </c>
@@ -40452,7 +40452,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="797" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A797" s="5">
         <v>409</v>
       </c>
@@ -41076,7 +41076,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="821" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A821" s="5">
         <v>424</v>
       </c>
@@ -41804,7 +41804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="849" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A849" s="5">
         <v>439</v>
       </c>
@@ -42064,7 +42064,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="859" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A859" s="5">
         <v>444</v>
       </c>
@@ -42480,7 +42480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="875" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A875" s="5">
         <v>452</v>
       </c>
@@ -42896,7 +42896,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="891" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A891" s="5">
         <v>460</v>
       </c>
@@ -44300,7 +44300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="945" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A945" s="5">
         <v>487</v>
       </c>
@@ -44404,7 +44404,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="949" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A949" s="5">
         <v>489</v>
       </c>
@@ -44456,7 +44456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="951" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A951" s="5">
         <v>490</v>
       </c>
@@ -44820,7 +44820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="965" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A965" s="5">
         <v>497</v>
       </c>
@@ -45028,7 +45028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="973" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A973" s="5">
         <v>501</v>
       </c>
@@ -45236,7 +45236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="981" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A981" s="5">
         <v>505</v>
       </c>
@@ -45340,7 +45340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="985" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A985" s="5">
         <v>507</v>
       </c>
@@ -45652,7 +45652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="997" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A997" s="5">
         <v>513</v>
       </c>
@@ -45704,7 +45704,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="999" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A999" s="5">
         <v>514</v>
       </c>
@@ -46536,7 +46536,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1031" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A1031" s="5">
         <v>530</v>
       </c>
@@ -46744,7 +46744,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1039" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A1039" s="5">
         <v>534</v>
       </c>
@@ -47264,7 +47264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1059" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1059" s="5">
         <v>544</v>
       </c>
@@ -47316,7 +47316,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1061" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1061" s="5">
         <v>545</v>
       </c>
@@ -47368,7 +47368,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1063" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1063" s="5">
         <v>546</v>
       </c>
@@ -47420,7 +47420,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1065" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1065" s="5">
         <v>547</v>
       </c>
@@ -47472,7 +47472,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1067" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1067" s="5">
         <v>548</v>
       </c>
@@ -47524,7 +47524,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1069" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1069" s="5">
         <v>549</v>
       </c>
@@ -47576,7 +47576,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1071" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1071" s="5">
         <v>550</v>
       </c>
@@ -47628,7 +47628,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1073" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1073" s="5">
         <v>551</v>
       </c>
@@ -47680,7 +47680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1075" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1075" s="5">
         <v>552</v>
       </c>
@@ -47732,7 +47732,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1077" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1077" s="5">
         <v>553</v>
       </c>
@@ -47784,7 +47784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1079" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1079" s="5">
         <v>554</v>
       </c>
@@ -48824,7 +48824,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1119" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A1119" s="5">
         <v>574</v>
       </c>
@@ -49240,7 +49240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1135" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1135" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A1135" s="5">
         <v>582</v>
       </c>
@@ -49656,7 +49656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1151" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A1151" s="5">
         <v>590</v>
       </c>
@@ -50332,7 +50332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1177" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1177" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1177" s="5">
         <v>603</v>
       </c>
@@ -50540,7 +50540,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1185" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1185" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A1185" s="5">
         <v>607</v>
       </c>
@@ -51216,7 +51216,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1211" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1211" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A1211" s="5">
         <v>621</v>
       </c>
@@ -51268,7 +51268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1213" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="1213" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A1213" s="5">
         <v>622</v>
       </c>
@@ -52672,7 +52672,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1267" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1267" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A1267" s="5">
         <v>649</v>
       </c>
@@ -52776,7 +52776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1271" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1271" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1271" s="5">
         <v>651</v>
       </c>
@@ -52828,7 +52828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1273" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="1273" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1273" s="5">
         <v>652</v>
       </c>
@@ -53452,7 +53452,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1297" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1297" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1297" s="5">
         <v>664</v>
       </c>
@@ -53608,7 +53608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1303" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="1303" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1303" s="5">
         <v>667</v>
       </c>
@@ -53764,7 +53764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1309" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1309" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A1309" s="5">
         <v>670</v>
       </c>
@@ -53868,7 +53868,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1313" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1313" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1313" s="5">
         <v>672</v>
       </c>
@@ -54544,7 +54544,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1339" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="1339" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A1339" s="5">
         <v>685</v>
       </c>
@@ -54596,7 +54596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1341" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="1341" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1341" s="5">
         <v>686</v>
       </c>
@@ -54856,7 +54856,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1351" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1351" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A1351" s="5">
         <v>691</v>
       </c>
@@ -55324,7 +55324,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1369" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1369" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A1369" s="5">
         <v>700</v>
       </c>
@@ -55532,7 +55532,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1377" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="1377" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A1377" s="5">
         <v>704</v>
       </c>
@@ -57612,7 +57612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1457" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1457" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A1457" s="5">
         <v>745</v>
       </c>
@@ -58704,7 +58704,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1499" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="1499" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1499" s="5">
         <v>766</v>
       </c>
@@ -58912,7 +58912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1507" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1507" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1507" s="5">
         <v>770</v>
       </c>
@@ -59692,7 +59692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1537" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1537" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A1537" s="5">
         <v>785</v>
       </c>
@@ -60784,7 +60784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1579" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1579" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1579" s="5">
         <v>806</v>
       </c>
@@ -61252,7 +61252,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1597" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="1597" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A1597" s="5">
         <v>815</v>
       </c>
@@ -61356,7 +61356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1601" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="1601" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1601" s="5">
         <v>817</v>
       </c>
@@ -61486,7 +61486,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1606" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+    <row r="1606" spans="1:8" ht="184.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1606" s="5">
         <v>820</v>
       </c>
@@ -61512,7 +61512,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1607" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="1607" spans="1:8" ht="64.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1607" s="5">
         <v>820</v>
       </c>
@@ -61720,7 +61720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1615" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1615" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A1615" s="5">
         <v>824</v>
       </c>
@@ -61824,7 +61824,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1619" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="1619" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1619" s="5">
         <v>826</v>
       </c>
@@ -62448,7 +62448,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1643" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="1643" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1643" s="5">
         <v>838</v>
       </c>
@@ -62708,7 +62708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1653" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1653" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A1653" s="5">
         <v>843</v>
       </c>
@@ -63228,7 +63228,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1673" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1673" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A1673" s="5">
         <v>853</v>
       </c>
@@ -63384,7 +63384,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1679" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1679" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A1679" s="5">
         <v>856</v>
       </c>
@@ -63644,7 +63644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1689" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1689" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1689" s="5">
         <v>861</v>
       </c>
@@ -63852,7 +63852,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1697" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="1697" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1697" s="5">
         <v>865</v>
       </c>
@@ -64060,7 +64060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1705" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="1705" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A1705" s="5">
         <v>869</v>
       </c>
@@ -64112,7 +64112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1707" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="1707" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A1707" s="5">
         <v>870</v>
       </c>
@@ -64632,7 +64632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1727" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="1727" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1727" s="5">
         <v>880</v>
       </c>
@@ -65048,7 +65048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1743" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1743" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1743" s="5">
         <v>888</v>
       </c>
@@ -65516,7 +65516,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1761" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="1761" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A1761" s="5">
         <v>897</v>
       </c>
@@ -65542,7 +65542,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1762" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1762" spans="1:8" ht="94.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1762" s="5">
         <v>898</v>
       </c>
@@ -65568,7 +65568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1763" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1763" spans="1:8" ht="79.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1763" s="5">
         <v>898</v>
       </c>
@@ -65672,7 +65672,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1767" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="1767" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1767" s="5">
         <v>900</v>
       </c>
@@ -65724,7 +65724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1769" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+    <row r="1769" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A1769" s="5">
         <v>901</v>
       </c>
@@ -65828,7 +65828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1773" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1773" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A1773" s="5">
         <v>903</v>
       </c>
@@ -65880,7 +65880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1775" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1775" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1775" s="5">
         <v>904</v>
       </c>
@@ -65984,7 +65984,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1779" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="1779" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1779" s="5">
         <v>906</v>
       </c>
@@ -66140,7 +66140,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1785" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="1785" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A1785" s="5">
         <v>909</v>
       </c>
@@ -66608,7 +66608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1803" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="1803" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1803" s="5">
         <v>918</v>
       </c>
@@ -66972,7 +66972,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1817" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1817" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1817" s="5">
         <v>925</v>
       </c>
@@ -67024,7 +67024,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1819" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1819" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1819" s="5">
         <v>926</v>
       </c>
@@ -67076,7 +67076,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1821" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1821" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A1821" s="5">
         <v>927</v>
       </c>
@@ -67804,7 +67804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1849" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="1849" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1849" s="5">
         <v>941</v>
       </c>
@@ -67854,7 +67854,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1851" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="1851" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1851" s="5">
         <v>942</v>
       </c>
@@ -68218,7 +68218,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1865" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="1865" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A1865" s="5">
         <v>949</v>
       </c>
@@ -68478,7 +68478,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1875" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1875" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1875" s="5">
         <v>954</v>
       </c>
@@ -68582,7 +68582,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1879" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1879" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A1879" s="5">
         <v>956</v>
       </c>
@@ -68634,7 +68634,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1881" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="1881" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1881" s="5">
         <v>957</v>
       </c>
@@ -68790,7 +68790,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1887" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="1887" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A1887" s="5">
         <v>960</v>
       </c>
@@ -68894,7 +68894,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1891" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="1891" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1891" s="5">
         <v>962</v>
       </c>
@@ -69145,6 +69145,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C1D07E6-A903-40C1-BB22-0B2235594EDA}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="191.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
